--- a/Master_Database.xlsx
+++ b/Master_Database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\project\SmartGuidenceBot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E69FD2-2C8F-47FD-83BD-E7B376A95E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C749F9-7D41-46FC-AB2F-53D4382D84C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curriculum" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="491">
   <si>
     <t>Grade_ID</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Activity</t>
-  </si>
-  <si>
-    <t>Activity1</t>
   </si>
   <si>
     <t>Page_Ref</t>
@@ -955,9 +952,6 @@
   </si>
   <si>
     <t>التعرف على الزاوية القائمة ومقارنتها</t>
-  </si>
-  <si>
-    <t>يأخذ التلميذ عصوين من أعواد البناء ويفتحهما ويسددهما لعمل زوايا حادة ومنفرجة وزاوية قائمة.</t>
   </si>
   <si>
     <t>تدوير العصا</t>
@@ -1279,72 +1273,25 @@
     <t>تعويد الطالب على فكرة (100 وحدة = 1 وحدة أكبر) تلقائياً.</t>
   </si>
   <si>
-    <t>1. الأدوات ألعاب نقدية وهمية أو قصاصات ورقية (تمثل 1 دينار، و10 دراهم، و1 درهم)، أو مكعبات (100 مكعب = مائة)
-2. المهمة يطلب المعلم من التلاميذ جمع مبلغين
-3. "لَدَى سَمْعَان 850 درهم، ولَدَى نَبْهانة 950 درهم، كم المجموع؟"
-4. يبدأ الطلاب بالجمع بالعد المباشر
-5. 0+0، 50+50، 800+900
-6. هنا يأتي دور "محل التبديل" بمجرد أن يصل مجموع الطلاب إلى 100 (مثلاً في خانة المئات أو عند جمع الدراهم)، يجب عليهم الذهاب إلى "محل التبديل" (أحد الزملاء) واستبدال المائة الزائدة بدينار واحد
-7. القيمة تربط اللعبة بين العملية الحسابية المجردة والعملية الحقيقية (الصرف)، مما يسهل عليهم فهم إعادة التجميع في مسائل الزمن (60 دقيقة = 1 ساعة) أو الأطوال (100 سم = 1 م)</t>
-  </si>
-  <si>
     <t>اللغز المترابط</t>
   </si>
   <si>
     <t>تدريب الطالب على عدم القفز إلى النتيجة النهائية مباشرة.</t>
   </si>
   <si>
-    <t>1. الأدوات بطاقات مسائل مقطعة
-2. يتم تقسيم المسألة المعقدة إلى بطاقتين، البطاقة 1 "اشترى فَهْمان حقيبة بـ9
-3. 450 د وحذاء بـ8 د
-4. ما ثمن الحقيبة والحذاء معاً؟" (الخطوة الأولى)
-5. البطاقة 2" بِكم يَقِلّ ثمنُ الحذاءِ عن ثمنِ الحقيبةِ؟" (الخطوة الثانية التي تعتمد على نتيجة البطاقة الأولى)
-6. يقوم الطلاب بحل البطاقة الأولى، ويسلمون الإجابة (الورقة الرابحة) لزميلهم ليستخدمها في حل البطاقة الثانية
-7. من يخطئ في البطاقة الأولى، لن يتمكن من حل الثانية
-8. القيمة تعلم الطلاب أن مسألة واحدة قد تحتوي على "سر" وهو أنه يجب عليك حل جزء منها لتفك الجزء الآخر</t>
-  </si>
-  <si>
     <t>من الأكثر إنفاقاً؟</t>
   </si>
   <si>
     <t>ترتيب العمليات الحسابية بشكل صحيح (حساب أ، حساب ب، ثم مقارنة أ - ب).</t>
   </si>
   <si>
-    <t>1. الأدوات لوحة سبورة ومسابقة بين فريقين (فريق "سَمْعان" وفريق "فَرْحَان")
-2. المسألة في الأسبوع الأول من العمل، ربح عَلِيٌّ 80 ديناراً يوم الأحد و 30 ديناراً يوم الإثنين
-3. في الأسبوع الثاني، ربح 50 ديناراً فقط يوم الخميس
-4. في أي أسبوع ربح أكثر؟ بكم؟"
-5. يقوم فريق سَمْعَان بحساب مجموع الأسبوع الأول
-6. يقوم فريق فَرْحَان بحساب مجموع الأسبوع الثاني
-7. تُكتب النتائجان على اللوحة، ويقوم الطلاب معاً بعملية الطرح (أكبر مجموع - أصغر مجموع)
-8. القيمة تظهر للطالب أن القفز إلى القراءة لا يكفي، بل يجب تنظيم البيانات في مجموعات منفصلة قبل المقارنة</t>
-  </si>
-  <si>
     <t>ساحر الوقت</t>
   </si>
   <si>
     <t>تخطي عقبة "60 دقيقة".</t>
   </si>
   <si>
-    <t>1. الأدوات ساعة كبيرة ومتحركة، وبطاقات عليها أرقام الدقائق
-2. يعرض المعلم المسألة
-3. يقوم الطلاب بحساب مجموع الدقائق أولاً (95 دقيقة)
-4. يضعون ساعة اصطناعية (أو يتحركون عقارب الساعة الكبيرة) من الساعة 12 إلى الساعة 1 (مما يمثل 60 دقيقة)
-5. السؤال "هل انتهت الدقائق الـ95؟" (الجواب لا)
-6. يلاحظون المتبقي (35 دقيقة)
-7. يضيفونها إلى عقرب الساعات
-8. القيمة المحاكاة الحركية للعقارب تساعد في تصور عملية "التحويل" التي لا تظهر بسهولة في الكتابة الرقمية المجردة</t>
-  </si>
-  <si>
     <t>التمييز السريع بين كلمات دالة على المحيط (سياج، شريط، سير) والمساحة (دهان، سجاد، بلاط).</t>
-  </si>
-  <si>
-    <t>1. الأدوات بطاقات مكتوب عليها مسائل قصيرة بدون أرقام
-2. طريقة يقرأ الطالب البطاقة "أراد فَرْحَان وضع سلكاً حول حديقة مستطيلة
-3. يصيح الطلاب بسرعة "محيط!" ويقومون بتقليد حركة وضع الأسلاك بأيديهم (دائرة حول أنفسهم)
-4. بطاقة أخرى "أراد فَهْمانة تبليط أرضية غرفته
-5. يصيح الطلاب "مساحة!" ويقومون بتقليد حركة وضع البلاط على الأرض (النزول ولمس الأرض)
-6. القيمة تربط الكلمات المفتاحية في المسألة اللفظية بالمفهوم الهندسي والوحدات الصحيحة (متر، متر مربع) قبل البدء بالحل</t>
   </si>
   <si>
     <t>تعويد الطفل على تعدد طرق تكوين المبلغ الواحد.</t>
@@ -1796,6 +1743,90 @@
 3. يقول المعلم "أريد استبدال هذه القطع العشرة بورقة واحدة فقط"
 4. يجب على الطالب أن يبحث عن ورقة الـ 1000 درهم (أو 1 دينار) ويسلمها للمعلم مقابل الحقيبة
 5. تكرر العملية عكسياً "أريد استبدال الـ 10 دنانير بعملات صغيرة"</t>
+  </si>
+  <si>
+    <t>Game_Templates</t>
+  </si>
+  <si>
+    <t>فردي</t>
+  </si>
+  <si>
+    <t>جماعي</t>
+  </si>
+  <si>
+    <t>بطاقة مكتوب عليها المسألة</t>
+  </si>
+  <si>
+    <t>صور أو بطاقات مرسومة تمثل المسألة</t>
+  </si>
+  <si>
+    <t>ألعاب نقدية وهمية أو قصاصات ورقية (تمثل 1 دينار، و100 دراهم، و100 درهم)، أو مكعبات (100 مكعب = مائة)</t>
+  </si>
+  <si>
+    <t>1. يتم تقسيم المسألة المعقدة إلى بطاقتين، البطاقة 1 "اشترى فَهْمان حقيبة بـ9
+2. 450 د وحذاء بـ8 د
+3. ما ثمن الحقيبة والحذاء معاً؟" (الخطوة الأولى)
+4. البطاقة 2" بِكم يَقِلّ ثمنُ الحذاءِ عن ثمنِ الحقيبةِ؟" (الخطوة الثانية التي تعتمد على نتيجة البطاقة الأولى)
+5. يقوم الطلاب بحل البطاقة الأولى، ويسلمون الإجابة (الورقة الرابحة) لزميلهم ليستخدمها في حل البطاقة الثانية
+6. من يخطئ في البطاقة الأولى، لن يتمكن من حل الثانية
+7. القيمة تعلم الطلاب أن مسألة واحدة قد تحتوي على "سر" وهو أنه يجب عليك حل جزء منها لتفك الجزء الآخر</t>
+  </si>
+  <si>
+    <t>1.  المهمة يطلب المعلم من التلاميذ جمع مبلغين
+2. "لَدَى سَمْعَان 850 درهم، ولَدَى نَبْهانة 950 درهم، كم المجموع؟"
+3. يبدأ الطلاب بالجمع بالعد المباشر
+4. 0+0، 50+50، 800+900
+5. هنا يأتي دور "محل التبديل" بمجرد أن يصل مجموع الطلاب إلى 100 (مثلاً في خانة المئات أو عند جمع الدراهم)، يجب عليهم الذهاب إلى "محل التبديل" (أحد الزملاء) واستبدال المائة الزائدة بدينار واحد
+6. القيمة تربط اللعبة بين العملية الحسابية المجردة والعملية الحقيقية (الصرف)، مما يسهل عليهم فهم إعادة التجميع في مسائل الزمن (60 دقيقة = 1 ساعة) أو الأطوال (100 سم = 1 م)</t>
+  </si>
+  <si>
+    <t>1. المسألة في الأسبوع الأول من العمل، ربح عَلِيٌّ 80 ديناراً يوم الأحد و 30 ديناراً يوم الإثنين
+2. في الأسبوع الثاني، ربح 50 ديناراً فقط يوم الخميس
+3. في أي أسبوع ربح أكثر؟ بكم؟"
+4. يقوم فريق سَمْعَان بحساب مجموع الأسبوع الأول
+5. يقوم فريق فَرْحَان بحساب مجموع الأسبوع الثاني
+6. تُكتب النتائجان على اللوحة، ويقوم الطلاب معاً بعملية الطرح (أكبر مجموع - أصغر مجموع)
+7. القيمة تظهر للطالب أن القفز إلى القراءة لا يكفي، بل يجب تنظيم البيانات في مجموعات منفصلة قبل المقارنة</t>
+  </si>
+  <si>
+    <t>1.  يعرض المعلم المسألة
+2. يقوم الطلاب بحساب مجموع الدقائق أولاً (95 دقيقة)
+3. يضعون ساعة اصطناعية (أو يتحركون عقارب الساعة الكبيرة) من الساعة 12 إلى الساعة 1 (مما يمثل 60 دقيقة)
+4. السؤال "هل انتهت الدقائق الـ95؟" (الجواب لا)
+5. يلاحظون المتبقي (35 دقيقة)
+6. يضيفونها إلى عقرب الساعات
+7. القيمة المحاكاة الحركية للعقارب تساعد في تصور عملية "التحويل" التي لا تظهر بسهولة في الكتابة الرقمية المجردة</t>
+  </si>
+  <si>
+    <t>1. طريقة يقرأ الطالب البطاقة "أراد فَرْحَان وضع سلكاً حول حديقة مستطيلة
+2. يصيح الطلاب بسرعة "محيط!" ويقومون بتقليد حركة وضع الأسلاك بأيديهم (دائرة حول أنفسهم)
+3. بطاقة أخرى "أراد فَهْمانة تبليط أرضية غرفته
+4. يصيح الطلاب "مساحة!" ويقومون بتقليد حركة وضع البلاط على الأرض (النزول ولمس الأرض)
+5. القيمة تربط الكلمات المفتاحية في المسألة اللفظية بالمفهوم الهندسي والوحدات الصحيحة (متر، متر مربع) قبل البدء بالحل</t>
+  </si>
+  <si>
+    <t>أيدي الطلاب</t>
+  </si>
+  <si>
+    <t>بطاقات مكتوب عليها مسائل قصيرة بدون أرقام</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> لوحة سبورة ومسابقة بين فريقين (فريق "سَمْعان" وفريق "فَرْحَان")</t>
+  </si>
+  <si>
+    <t>ساعة كبيرة ومتحركة، وبطاقات عليها أرقام الدقائق</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بطاقات مسائل مقطعة</t>
+  </si>
+  <si>
+    <t>Dificulty</t>
+  </si>
+  <si>
+    <t>Preferred_Game</t>
+  </si>
+  <si>
+    <t>1. يأخذ التلميذ عصوين من أعواد البناء ويفتحهما ويسددهما لعمل زوايا حادة ومنفرجة وزاوية قائمة.</t>
   </si>
 </sst>
 </file>
@@ -2159,21 +2190,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="168.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="168.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2190,1363 +2222,1492 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="H7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" t="s">
-        <v>69</v>
-      </c>
-      <c r="J9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" t="s">
-        <v>88</v>
-      </c>
-      <c r="I12" t="s">
-        <v>89</v>
-      </c>
-      <c r="J12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" t="s">
+        <v>108</v>
+      </c>
+      <c r="J15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>94</v>
-      </c>
-      <c r="H13" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" t="s">
+        <v>115</v>
+      </c>
+      <c r="J16" t="s">
+        <v>116</v>
+      </c>
+      <c r="K16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" t="s">
+        <v>123</v>
+      </c>
+      <c r="K17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" t="s">
+        <v>129</v>
+      </c>
+      <c r="K18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J19" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" t="s">
+        <v>142</v>
+      </c>
+      <c r="J20" t="s">
+        <v>143</v>
+      </c>
+      <c r="K20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s">
+        <v>148</v>
+      </c>
+      <c r="I21" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" t="s">
+        <v>150</v>
+      </c>
+      <c r="K21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" t="s">
+        <v>156</v>
+      </c>
+      <c r="J22" t="s">
+        <v>157</v>
+      </c>
+      <c r="K22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" t="s">
+        <v>160</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" t="s">
+        <v>163</v>
+      </c>
+      <c r="K23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="D24" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s">
+        <v>167</v>
+      </c>
+      <c r="I24" t="s">
+        <v>168</v>
+      </c>
+      <c r="J24" t="s">
+        <v>169</v>
+      </c>
+      <c r="K24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>181</v>
+      </c>
+      <c r="I26" t="s">
+        <v>182</v>
+      </c>
+      <c r="J26" t="s">
+        <v>183</v>
+      </c>
+      <c r="K26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" t="s">
+        <v>187</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s">
+        <v>188</v>
+      </c>
+      <c r="I27" t="s">
+        <v>189</v>
+      </c>
+      <c r="J27" t="s">
+        <v>190</v>
+      </c>
+      <c r="K27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28" t="s">
+        <v>194</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s">
+        <v>195</v>
+      </c>
+      <c r="I28" t="s">
+        <v>196</v>
+      </c>
+      <c r="J28" t="s">
+        <v>197</v>
+      </c>
+      <c r="K28" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" t="s">
+        <v>201</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29" t="s">
+        <v>203</v>
+      </c>
+      <c r="J29" t="s">
+        <v>204</v>
+      </c>
+      <c r="K29" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" t="s">
+        <v>208</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>209</v>
+      </c>
+      <c r="I30" t="s">
+        <v>210</v>
+      </c>
+      <c r="J30" t="s">
+        <v>211</v>
+      </c>
+      <c r="K30" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" t="s">
+        <v>213</v>
+      </c>
+      <c r="D31" t="s">
+        <v>214</v>
+      </c>
+      <c r="E31" t="s">
+        <v>215</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" t="s">
+        <v>217</v>
+      </c>
+      <c r="J31" t="s">
+        <v>218</v>
+      </c>
+      <c r="K31" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" t="s">
+        <v>220</v>
+      </c>
+      <c r="D32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E32" t="s">
+        <v>222</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" t="s">
+        <v>223</v>
+      </c>
+      <c r="I32" t="s">
+        <v>224</v>
+      </c>
+      <c r="J32" t="s">
+        <v>225</v>
+      </c>
+      <c r="K32" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>227</v>
+      </c>
+      <c r="B33" t="s">
+        <v>228</v>
+      </c>
+      <c r="C33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" t="s">
+        <v>231</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" t="s">
+        <v>232</v>
+      </c>
+      <c r="I33" t="s">
+        <v>233</v>
+      </c>
+      <c r="J33" t="s">
+        <v>234</v>
+      </c>
+      <c r="K33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" t="s">
+        <v>228</v>
+      </c>
+      <c r="C34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" t="s">
+        <v>238</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" t="s">
+        <v>239</v>
+      </c>
+      <c r="I34" t="s">
+        <v>240</v>
+      </c>
+      <c r="J34" t="s">
+        <v>241</v>
+      </c>
+      <c r="K34" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" t="s">
+        <v>243</v>
+      </c>
+      <c r="D35" t="s">
+        <v>244</v>
+      </c>
+      <c r="E35" t="s">
+        <v>245</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s">
+        <v>246</v>
+      </c>
+      <c r="I35" t="s">
+        <v>247</v>
+      </c>
+      <c r="J35" t="s">
+        <v>248</v>
+      </c>
+      <c r="K35" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" t="s">
+        <v>228</v>
+      </c>
+      <c r="C36" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" t="s">
+        <v>251</v>
+      </c>
+      <c r="E36" t="s">
+        <v>252</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>253</v>
+      </c>
+      <c r="I36" t="s">
+        <v>254</v>
+      </c>
+      <c r="J36" t="s">
+        <v>241</v>
+      </c>
+      <c r="K36" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" t="s">
+        <v>256</v>
+      </c>
+      <c r="D37" t="s">
+        <v>257</v>
+      </c>
+      <c r="E37" t="s">
+        <v>258</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
+        <v>259</v>
+      </c>
+      <c r="I37" t="s">
+        <v>260</v>
+      </c>
+      <c r="J37" t="s">
+        <v>241</v>
+      </c>
+      <c r="K37" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" t="s">
+        <v>262</v>
+      </c>
+      <c r="D38" t="s">
+        <v>263</v>
+      </c>
+      <c r="E38" t="s">
+        <v>264</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
+        <v>265</v>
+      </c>
+      <c r="I38" t="s">
+        <v>266</v>
+      </c>
+      <c r="J38" t="s">
+        <v>267</v>
+      </c>
+      <c r="K38" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" t="s">
+        <v>269</v>
+      </c>
+      <c r="D39" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" t="s">
+        <v>271</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s">
+        <v>272</v>
+      </c>
+      <c r="I39" t="s">
+        <v>273</v>
+      </c>
+      <c r="J39" t="s">
+        <v>274</v>
+      </c>
+      <c r="K39" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>227</v>
+      </c>
+      <c r="B40" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I15" t="s">
-        <v>110</v>
-      </c>
-      <c r="J15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" t="s">
-        <v>114</v>
-      </c>
-      <c r="F16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" t="s">
-        <v>115</v>
-      </c>
-      <c r="H16" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" t="s">
-        <v>117</v>
-      </c>
-      <c r="J16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" t="s">
-        <v>123</v>
-      </c>
-      <c r="I17" t="s">
-        <v>124</v>
-      </c>
-      <c r="J17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" t="s">
-        <v>123</v>
-      </c>
-      <c r="I18" t="s">
-        <v>130</v>
-      </c>
-      <c r="J18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D19" t="s">
-        <v>133</v>
-      </c>
-      <c r="E19" t="s">
-        <v>134</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C20" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" t="s">
-        <v>141</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" t="s">
-        <v>143</v>
-      </c>
-      <c r="I20" t="s">
-        <v>144</v>
-      </c>
-      <c r="J20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" t="s">
-        <v>150</v>
-      </c>
-      <c r="I21" t="s">
-        <v>151</v>
-      </c>
-      <c r="J21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" t="s">
-        <v>155</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>156</v>
-      </c>
-      <c r="H22" t="s">
-        <v>157</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-      <c r="J22" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23" t="s">
-        <v>161</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" t="s">
-        <v>163</v>
-      </c>
-      <c r="I23" t="s">
-        <v>164</v>
-      </c>
-      <c r="J23" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>168</v>
-      </c>
-      <c r="H24" t="s">
-        <v>169</v>
-      </c>
-      <c r="I24" t="s">
-        <v>170</v>
-      </c>
-      <c r="J24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" t="s">
-        <v>173</v>
-      </c>
-      <c r="E25" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" t="s">
-        <v>177</v>
-      </c>
-      <c r="J25" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" t="s">
-        <v>180</v>
-      </c>
-      <c r="E26" t="s">
-        <v>181</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
-        <v>182</v>
-      </c>
-      <c r="H26" t="s">
-        <v>183</v>
-      </c>
-      <c r="I26" t="s">
-        <v>184</v>
-      </c>
-      <c r="J26" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" t="s">
-        <v>187</v>
-      </c>
-      <c r="E27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" t="s">
-        <v>189</v>
-      </c>
-      <c r="H27" t="s">
-        <v>190</v>
-      </c>
-      <c r="I27" t="s">
-        <v>191</v>
-      </c>
-      <c r="J27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" t="s">
-        <v>195</v>
-      </c>
-      <c r="F28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" t="s">
-        <v>196</v>
-      </c>
-      <c r="H28" t="s">
-        <v>197</v>
-      </c>
-      <c r="I28" t="s">
-        <v>198</v>
-      </c>
-      <c r="J28" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" t="s">
-        <v>200</v>
-      </c>
-      <c r="D29" t="s">
-        <v>201</v>
-      </c>
-      <c r="E29" t="s">
-        <v>202</v>
-      </c>
-      <c r="F29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" t="s">
-        <v>203</v>
-      </c>
-      <c r="H29" t="s">
-        <v>204</v>
-      </c>
-      <c r="I29" t="s">
-        <v>205</v>
-      </c>
-      <c r="J29" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" t="s">
-        <v>207</v>
-      </c>
-      <c r="D30" t="s">
-        <v>208</v>
-      </c>
-      <c r="E30" t="s">
-        <v>209</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
-        <v>210</v>
-      </c>
-      <c r="H30" t="s">
-        <v>211</v>
-      </c>
-      <c r="I30" t="s">
-        <v>212</v>
-      </c>
-      <c r="J30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" t="s">
-        <v>127</v>
-      </c>
-      <c r="C31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D31" t="s">
-        <v>215</v>
-      </c>
-      <c r="E31" t="s">
-        <v>216</v>
-      </c>
-      <c r="F31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" t="s">
-        <v>217</v>
-      </c>
-      <c r="H31" t="s">
-        <v>218</v>
-      </c>
-      <c r="I31" t="s">
-        <v>219</v>
-      </c>
-      <c r="J31" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>126</v>
-      </c>
-      <c r="B32" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" t="s">
-        <v>221</v>
-      </c>
-      <c r="D32" t="s">
-        <v>222</v>
-      </c>
-      <c r="E32" t="s">
-        <v>223</v>
-      </c>
-      <c r="F32" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" t="s">
-        <v>224</v>
-      </c>
-      <c r="H32" t="s">
-        <v>225</v>
-      </c>
-      <c r="I32" t="s">
-        <v>226</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="D40" t="s">
+        <v>276</v>
+      </c>
+      <c r="E40" t="s">
+        <v>277</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s">
+        <v>278</v>
+      </c>
+      <c r="I40" t="s">
+        <v>279</v>
+      </c>
+      <c r="J40" t="s">
+        <v>280</v>
+      </c>
+      <c r="K40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B41" t="s">
         <v>228</v>
       </c>
-      <c r="B33" t="s">
-        <v>229</v>
-      </c>
-      <c r="C33" t="s">
-        <v>230</v>
-      </c>
-      <c r="D33" t="s">
-        <v>231</v>
-      </c>
-      <c r="E33" t="s">
-        <v>232</v>
-      </c>
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" t="s">
-        <v>233</v>
-      </c>
-      <c r="H33" t="s">
-        <v>234</v>
-      </c>
-      <c r="I33" t="s">
-        <v>235</v>
-      </c>
-      <c r="J33" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="C41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D41" t="s">
+        <v>283</v>
+      </c>
+      <c r="E41" t="s">
+        <v>284</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>490</v>
+      </c>
+      <c r="I41" t="s">
+        <v>285</v>
+      </c>
+      <c r="J41" t="s">
+        <v>286</v>
+      </c>
+      <c r="K41" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>227</v>
+      </c>
+      <c r="B42" t="s">
         <v>228</v>
       </c>
-      <c r="B34" t="s">
-        <v>229</v>
-      </c>
-      <c r="C34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D34" t="s">
-        <v>238</v>
-      </c>
-      <c r="E34" t="s">
-        <v>239</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H34" t="s">
-        <v>241</v>
-      </c>
-      <c r="I34" t="s">
-        <v>242</v>
-      </c>
-      <c r="J34" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="C42" t="s">
+        <v>288</v>
+      </c>
+      <c r="D42" t="s">
+        <v>289</v>
+      </c>
+      <c r="E42" t="s">
+        <v>290</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s">
+        <v>291</v>
+      </c>
+      <c r="I42" t="s">
+        <v>292</v>
+      </c>
+      <c r="J42" t="s">
+        <v>293</v>
+      </c>
+      <c r="K42" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>227</v>
+      </c>
+      <c r="B43" t="s">
         <v>228</v>
       </c>
-      <c r="B35" t="s">
-        <v>229</v>
-      </c>
-      <c r="C35" t="s">
-        <v>244</v>
-      </c>
-      <c r="D35" t="s">
-        <v>245</v>
-      </c>
-      <c r="E35" t="s">
-        <v>246</v>
-      </c>
-      <c r="F35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" t="s">
-        <v>247</v>
-      </c>
-      <c r="H35" t="s">
-        <v>248</v>
-      </c>
-      <c r="I35" t="s">
-        <v>249</v>
-      </c>
-      <c r="J35" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>228</v>
-      </c>
-      <c r="B36" t="s">
-        <v>229</v>
-      </c>
-      <c r="C36" t="s">
-        <v>251</v>
-      </c>
-      <c r="D36" t="s">
-        <v>252</v>
-      </c>
-      <c r="E36" t="s">
-        <v>253</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" t="s">
-        <v>254</v>
-      </c>
-      <c r="H36" t="s">
-        <v>255</v>
-      </c>
-      <c r="I36" t="s">
-        <v>242</v>
-      </c>
-      <c r="J36" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>228</v>
-      </c>
-      <c r="B37" t="s">
-        <v>229</v>
-      </c>
-      <c r="C37" t="s">
-        <v>257</v>
-      </c>
-      <c r="D37" t="s">
-        <v>258</v>
-      </c>
-      <c r="E37" t="s">
-        <v>259</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
-        <v>260</v>
-      </c>
-      <c r="H37" t="s">
-        <v>261</v>
-      </c>
-      <c r="I37" t="s">
-        <v>242</v>
-      </c>
-      <c r="J37" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>228</v>
-      </c>
-      <c r="B38" t="s">
-        <v>229</v>
-      </c>
-      <c r="C38" t="s">
-        <v>263</v>
-      </c>
-      <c r="D38" t="s">
-        <v>264</v>
-      </c>
-      <c r="E38" t="s">
-        <v>265</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>266</v>
-      </c>
-      <c r="H38" t="s">
-        <v>267</v>
-      </c>
-      <c r="I38" t="s">
-        <v>268</v>
-      </c>
-      <c r="J38" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B39" t="s">
-        <v>229</v>
-      </c>
-      <c r="C39" t="s">
-        <v>270</v>
-      </c>
-      <c r="D39" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" t="s">
-        <v>272</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" t="s">
-        <v>273</v>
-      </c>
-      <c r="H39" t="s">
-        <v>274</v>
-      </c>
-      <c r="I39" t="s">
-        <v>275</v>
-      </c>
-      <c r="J39" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>228</v>
-      </c>
-      <c r="B40" t="s">
-        <v>229</v>
-      </c>
-      <c r="C40" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" t="s">
-        <v>277</v>
-      </c>
-      <c r="E40" t="s">
-        <v>278</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" t="s">
-        <v>279</v>
-      </c>
-      <c r="H40" t="s">
-        <v>280</v>
-      </c>
-      <c r="I40" t="s">
-        <v>281</v>
-      </c>
-      <c r="J40" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>228</v>
-      </c>
-      <c r="B41" t="s">
-        <v>229</v>
-      </c>
-      <c r="C41" t="s">
-        <v>283</v>
-      </c>
-      <c r="D41" t="s">
-        <v>284</v>
-      </c>
-      <c r="E41" t="s">
-        <v>285</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" t="s">
-        <v>286</v>
-      </c>
-      <c r="H41" t="s">
-        <v>287</v>
-      </c>
-      <c r="I41" t="s">
-        <v>288</v>
-      </c>
-      <c r="J41" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>228</v>
-      </c>
-      <c r="B42" t="s">
-        <v>229</v>
-      </c>
-      <c r="C42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D42" t="s">
-        <v>291</v>
-      </c>
-      <c r="E42" t="s">
-        <v>292</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" t="s">
-        <v>293</v>
-      </c>
-      <c r="H42" t="s">
-        <v>294</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="C43" t="s">
         <v>295</v>
       </c>
-      <c r="J42" t="s">
+      <c r="D43" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>228</v>
-      </c>
-      <c r="B43" t="s">
-        <v>229</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="E43" t="s">
         <v>297</v>
       </c>
-      <c r="D43" t="s">
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
         <v>298</v>
       </c>
-      <c r="E43" t="s">
+      <c r="I43" t="s">
         <v>299</v>
       </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="J43" t="s">
         <v>300</v>
       </c>
-      <c r="H43" t="s">
+      <c r="K43" t="s">
         <v>301</v>
-      </c>
-      <c r="I43" t="s">
-        <v>302</v>
-      </c>
-      <c r="J43" t="s">
-        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -3556,773 +3717,966 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="255.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="84.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>305</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>307</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
         <v>308</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D3" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>310</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>311</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D4" t="s">
         <v>313</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>314</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
         <v>315</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" t="s">
+        <v>474</v>
+      </c>
+      <c r="D5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>317</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
         <v>318</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C6" t="s">
+        <v>473</v>
+      </c>
+      <c r="D6" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>320</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
         <v>321</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D7" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>323</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s">
         <v>324</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C8" t="s">
+        <v>474</v>
+      </c>
+      <c r="D8" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>326</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
         <v>327</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C9" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
         <v>329</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" t="s">
         <v>330</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C10" t="s">
+        <v>474</v>
+      </c>
+      <c r="D10" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>332</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>333</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B11" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D11" t="s">
         <v>335</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
         <v>336</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>337</v>
       </c>
-      <c r="D11" t="s">
+      <c r="B12" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
+        <v>474</v>
+      </c>
+      <c r="D12" t="s">
+        <v>475</v>
+      </c>
+      <c r="E12" t="s">
         <v>339</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>340</v>
       </c>
-      <c r="D12" t="s">
+      <c r="B13" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C13" t="s">
+        <v>474</v>
+      </c>
+      <c r="D13" t="s">
+        <v>476</v>
+      </c>
+      <c r="E13" t="s">
         <v>342</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" t="s">
         <v>343</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C14" t="s">
+        <v>474</v>
+      </c>
+      <c r="D14" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
         <v>345</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>241</v>
+      </c>
+      <c r="B15" t="s">
         <v>346</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C15" t="s">
+        <v>474</v>
+      </c>
+      <c r="D15" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>242</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="E15" t="s">
         <v>348</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" t="s">
         <v>349</v>
       </c>
-      <c r="D15" t="s">
+      <c r="C16" t="s">
+        <v>473</v>
+      </c>
+      <c r="D16" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>275</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="E16" t="s">
         <v>351</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>280</v>
+      </c>
+      <c r="B17" t="s">
         <v>352</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C17" t="s">
+        <v>473</v>
+      </c>
+      <c r="D17" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>281</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="E17" t="s">
         <v>354</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B18" t="s">
         <v>355</v>
       </c>
-      <c r="D17" t="s">
+      <c r="C18" t="s">
+        <v>473</v>
+      </c>
+      <c r="D18" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="E18" t="s">
         <v>357</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>293</v>
+      </c>
+      <c r="B19" t="s">
         <v>358</v>
       </c>
-      <c r="D18" t="s">
+      <c r="C19" t="s">
+        <v>473</v>
+      </c>
+      <c r="D19" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>295</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="E19" t="s">
         <v>360</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B20" t="s">
         <v>361</v>
       </c>
-      <c r="D19" t="s">
+      <c r="C20" t="s">
+        <v>474</v>
+      </c>
+      <c r="D20" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>268</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="E20" t="s">
         <v>363</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>364</v>
       </c>
-      <c r="D20" t="s">
+      <c r="B21" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C21" t="s">
+        <v>473</v>
+      </c>
+      <c r="D21" t="s">
+        <v>477</v>
+      </c>
+      <c r="E21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>366</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>367</v>
       </c>
-      <c r="D21" t="s">
+      <c r="C22" t="s">
+        <v>474</v>
+      </c>
+      <c r="D22" t="s">
+        <v>487</v>
+      </c>
+      <c r="E22" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
         <v>369</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C23" t="s">
+        <v>474</v>
+      </c>
+      <c r="D23" t="s">
+        <v>485</v>
+      </c>
+      <c r="E23" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>370</v>
       </c>
-      <c r="D22" t="s">
+      <c r="B24" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C24" t="s">
+        <v>474</v>
+      </c>
+      <c r="D24" t="s">
+        <v>486</v>
+      </c>
+      <c r="E24" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>300</v>
+      </c>
+      <c r="B25" t="s">
         <v>372</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C25" t="s">
+        <v>473</v>
+      </c>
+      <c r="D25" t="s">
+        <v>484</v>
+      </c>
+      <c r="E25" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s">
         <v>373</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C26" t="s">
+        <v>474</v>
+      </c>
+      <c r="D26" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="E26" t="s">
         <v>375</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" t="s">
         <v>376</v>
       </c>
-      <c r="D24" t="s">
+      <c r="C27" t="s">
+        <v>474</v>
+      </c>
+      <c r="D27" t="s">
+        <v>470</v>
+      </c>
+      <c r="E27" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>302</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C28" t="s">
+        <v>474</v>
+      </c>
+      <c r="D28" t="s">
         <v>378</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E28" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>380</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B29" t="s">
         <v>381</v>
       </c>
-      <c r="D26" t="s">
+      <c r="C29" t="s">
+        <v>474</v>
+      </c>
+      <c r="D29" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="E29" t="s">
         <v>383</v>
       </c>
-      <c r="C27" t="s">
-        <v>477</v>
-      </c>
-      <c r="D27" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>144</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" t="s">
         <v>384</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C30" t="s">
+        <v>473</v>
+      </c>
+      <c r="D30" t="s">
         <v>385</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E30" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" t="s">
         <v>387</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C31" t="s">
+        <v>474</v>
+      </c>
+      <c r="D31" t="s">
+        <v>483</v>
+      </c>
+      <c r="E31" t="s">
         <v>388</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" t="s">
         <v>389</v>
       </c>
-      <c r="D29" t="s">
+      <c r="C32" t="s">
+        <v>474</v>
+      </c>
+      <c r="D32" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="E32" t="s">
         <v>391</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" t="s">
         <v>392</v>
       </c>
-      <c r="D30" t="s">
+      <c r="C33" t="s">
+        <v>473</v>
+      </c>
+      <c r="D33" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>158</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="E33" t="s">
         <v>394</v>
       </c>
-      <c r="D31" t="s">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>396</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C34" t="s">
+        <v>473</v>
+      </c>
+      <c r="D34" t="s">
         <v>397</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E34" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>177</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>399</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B35" t="s">
         <v>400</v>
       </c>
-      <c r="D33" t="s">
+      <c r="C35" t="s">
+        <v>473</v>
+      </c>
+      <c r="D35" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="E35" t="s">
         <v>402</v>
       </c>
-      <c r="B34" t="s">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
         <v>403</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C36" t="s">
+        <v>474</v>
+      </c>
+      <c r="D36" t="s">
         <v>404</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E36" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" t="s">
         <v>406</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C37" t="s">
+        <v>474</v>
+      </c>
+      <c r="D37" t="s">
         <v>407</v>
       </c>
-      <c r="C35" t="s">
+      <c r="E37" t="s">
         <v>408</v>
       </c>
-      <c r="D35" t="s">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C38" t="s">
+        <v>474</v>
+      </c>
+      <c r="D38" t="s">
         <v>410</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E38" t="s">
         <v>411</v>
       </c>
-      <c r="D36" t="s">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>184</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="C39" t="s">
+        <v>473</v>
+      </c>
+      <c r="D39" t="s">
         <v>413</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E39" t="s">
         <v>414</v>
       </c>
-      <c r="D37" t="s">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>211</v>
+      </c>
+      <c r="B40" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>198</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C40" t="s">
+        <v>473</v>
+      </c>
+      <c r="D40" t="s">
         <v>416</v>
       </c>
-      <c r="C38" t="s">
+      <c r="E40" t="s">
         <v>417</v>
       </c>
-      <c r="D38" t="s">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>205</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="B41" t="s">
         <v>419</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C41" t="s">
+        <v>473</v>
+      </c>
+      <c r="D41" t="s">
         <v>420</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E41" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>212</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>225</v>
+      </c>
+      <c r="B42" t="s">
         <v>422</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C42" t="s">
+        <v>473</v>
+      </c>
+      <c r="D42" t="s">
         <v>423</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E42" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" t="s">
         <v>425</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C43" t="s">
+        <v>473</v>
+      </c>
+      <c r="D43" t="s">
         <v>426</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E43" t="s">
         <v>427</v>
       </c>
-      <c r="D41" t="s">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>226</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="B44" t="s">
         <v>429</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C44" t="s">
+        <v>473</v>
+      </c>
+      <c r="D44" t="s">
         <v>430</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E44" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>432</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B45" t="s">
         <v>433</v>
       </c>
-      <c r="D43" t="s">
+      <c r="C45" t="s">
+        <v>473</v>
+      </c>
+      <c r="D45" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="E45" t="s">
         <v>435</v>
       </c>
-      <c r="B44" t="s">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>436</v>
       </c>
-      <c r="C44" t="s">
+      <c r="B46" t="s">
         <v>437</v>
       </c>
-      <c r="D44" t="s">
+      <c r="C46" t="s">
+        <v>473</v>
+      </c>
+      <c r="D46" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="E46" t="s">
         <v>439</v>
       </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>248</v>
+      </c>
+      <c r="B47" t="s">
         <v>440</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C47" t="s">
+        <v>474</v>
+      </c>
+      <c r="D47" t="s">
         <v>441</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E47" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>169</v>
+      </c>
+      <c r="B48" t="s">
         <v>443</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C48" t="s">
+        <v>474</v>
+      </c>
+      <c r="D48" t="s">
         <v>444</v>
       </c>
-      <c r="C46" t="s">
+      <c r="E48" t="s">
         <v>445</v>
       </c>
-      <c r="D46" t="s">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>249</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="C49" t="s">
+        <v>474</v>
+      </c>
+      <c r="D49" t="s">
         <v>447</v>
       </c>
-      <c r="C47" t="s">
+      <c r="E49" t="s">
         <v>448</v>
       </c>
-      <c r="D47" t="s">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>170</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="C50" t="s">
+        <v>474</v>
+      </c>
+      <c r="D50" t="s">
         <v>450</v>
       </c>
-      <c r="C48" t="s">
+      <c r="E50" t="s">
         <v>451</v>
       </c>
-      <c r="D48" t="s">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>25</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="C51" t="s">
+        <v>473</v>
+      </c>
+      <c r="D51" t="s">
         <v>453</v>
       </c>
-      <c r="C49" t="s">
+      <c r="E51" t="s">
         <v>454</v>
       </c>
-      <c r="D49" t="s">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="C52" t="s">
+        <v>474</v>
+      </c>
+      <c r="D52" t="s">
         <v>456</v>
       </c>
-      <c r="C50" t="s">
+      <c r="E52" t="s">
         <v>457</v>
       </c>
-      <c r="D50" t="s">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="C53" t="s">
+        <v>474</v>
+      </c>
+      <c r="D53" t="s">
         <v>459</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E53" t="s">
         <v>460</v>
       </c>
-      <c r="D51" t="s">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C54" t="s">
+        <v>473</v>
+      </c>
+      <c r="D54" t="s">
         <v>462</v>
       </c>
-      <c r="C52" t="s">
+      <c r="E54" t="s">
         <v>463</v>
       </c>
-      <c r="D52" t="s">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C55" t="s">
+        <v>473</v>
+      </c>
+      <c r="D55" t="s">
         <v>465</v>
       </c>
-      <c r="C53" t="s">
+      <c r="E55" t="s">
         <v>466</v>
       </c>
-      <c r="D53" t="s">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C56" t="s">
+        <v>474</v>
+      </c>
+      <c r="D56" t="s">
         <v>468</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E56" t="s">
         <v>469</v>
-      </c>
-      <c r="D54" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" t="s">
-        <v>471</v>
-      </c>
-      <c r="C55" t="s">
-        <v>472</v>
-      </c>
-      <c r="D55" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>117</v>
-      </c>
-      <c r="B56" t="s">
-        <v>474</v>
-      </c>
-      <c r="C56" t="s">
-        <v>475</v>
-      </c>
-      <c r="D56" t="s">
-        <v>476</v>
       </c>
     </row>
   </sheetData>
